--- a/查手机-上限与刷新对照表.xlsx
+++ b/查手机-上限与刷新对照表.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>默认原样沿用；一次刷新最多真改 2 项，多的回填旧值</t>
+          <t>默认原样沿用；一次刷新最多真改 4 项，多的回填旧值</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>默认沿用；一次最多真改 2 项，多的回填旧值</t>
+          <t>默认沿用；一次最多真改 4 项，多的回填旧值</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2 项</t>
+          <t>4 项（每个 app 各一个额度）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
